--- a/jpcore-r4b/develop/ValueSet-jp-medication-example-sitecomment-vs.xlsx
+++ b/jpcore-r4b/develop/ValueSet-jp-medication-example-sitecomment-vs.xlsx
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/jpcore-r4b/develop/ValueSet-jp-medication-example-sitecomment-vs.xlsx
+++ b/jpcore-r4b/develop/ValueSet-jp-medication-example-sitecomment-vs.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from JP Core Medicati" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
